--- a/api_football/Included League Starts.xlsx
+++ b/api_football/Included League Starts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greg\Matchday Insights\api_football\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCD4689-CFC5-4C67-9D19-818939003658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1289E940-AC47-41A9-AC89-DCE7F8F868B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{580AECB1-B849-4CA1-A1B4-08ABF84E37DB}"/>
   </bookViews>
@@ -216,9 +216,6 @@
     <t>MLT</t>
   </si>
   <si>
-    <t>MLD</t>
-  </si>
-  <si>
     <t>MKD</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>GEO</t>
   </si>
   <si>
-    <t>GBR</t>
-  </si>
-  <si>
     <t>FRO</t>
   </si>
   <si>
@@ -774,9 +768,6 @@
     <t>THA</t>
   </si>
   <si>
-    <t>TJK</t>
-  </si>
-  <si>
     <t>TKM</t>
   </si>
   <si>
@@ -973,6 +964,15 @@
   </si>
   <si>
     <t>POR_4</t>
+  </si>
+  <si>
+    <t>TAJ</t>
+  </si>
+  <si>
+    <t>GIB</t>
+  </si>
+  <si>
+    <t>MOL</t>
   </si>
 </sst>
 </file>
@@ -1434,30 +1434,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="6" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>87</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2">
         <f t="shared" ref="B2:G2" si="0">2.5/10</f>
@@ -1486,7 +1486,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2">
         <f>1.5/8</f>
@@ -1515,7 +1515,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2">
         <f>2/10</f>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2">
         <f t="shared" ref="B5:G5" si="1">1/12</f>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2">
         <f>1.5/18</f>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2">
         <f>1/8</f>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2">
         <f>3/12</f>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <f>3.5/16</f>
@@ -1741,7 +1741,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B12" s="2">
         <f>2.5/14</f>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2">
         <f t="shared" ref="B13:G13" si="2">1/10</f>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2">
         <f>3/18</f>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2">
         <f>4/14</f>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2">
         <f>3/18</f>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2">
         <f>2/14</f>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2">
         <f t="shared" ref="B18:G18" si="3">2/12</f>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <f t="shared" ref="B20:G20" si="4">3/20</f>
@@ -1978,7 +1978,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="2">
         <f t="shared" ref="B21:G21" si="5">3/24</f>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2">
         <f t="shared" ref="B22:G22" si="6">4/24</f>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2">
         <f t="shared" ref="B23:G23" si="7">2/24</f>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2">
         <f t="shared" ref="B24:G24" si="8">3/20</f>
@@ -2094,7 +2094,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2">
         <f t="shared" ref="B25:G25" si="9">4/22</f>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2">
         <f>62/102</f>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2">
         <f>108/396</f>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" s="2">
         <f>1.5/10</f>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B29" s="2">
         <f t="shared" ref="B29:G29" si="10">1.5/12</f>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2">
         <f>2.5/20</f>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2">
         <f>2.5/20</f>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B32" s="2">
         <f>1/18</f>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="2">
         <f>2/10</f>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>46</v>
+        <v>275</v>
       </c>
       <c r="B35" s="2">
         <f>0/11</f>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="2">
         <f t="shared" ref="B36:G36" si="11">2/10</f>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2">
         <f t="shared" ref="B37:D38" si="12">2.5/18</f>
@@ -2456,7 +2456,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="2">
         <f t="shared" si="12"/>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2">
         <f t="shared" ref="B39:G39" si="14">4/20</f>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
         <f>5/102</f>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2">
         <f>1.5/14</f>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="2">
         <f>2/12</f>
@@ -2601,7 +2601,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="2">
         <f>2/12</f>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B44" s="2">
         <f t="shared" ref="B44:G44" si="15">1.5/10</f>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" s="2">
         <f t="shared" ref="B45:G45" si="16">2/12</f>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B46" s="2">
         <f t="shared" ref="B46:G46" si="17">2/14</f>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B47" s="2">
         <f t="shared" ref="B47:G47" si="18">3/20</f>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="2">
         <f>3/20</f>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B49" s="2">
         <f>11/60</f>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" s="2">
         <f>15/166</f>
@@ -2832,7 +2832,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B51" s="2">
         <f>2/12</f>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B52" s="2">
         <f t="shared" ref="B52:G52" si="19">2.5/10</f>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B53" s="2">
         <f>0/6</f>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" s="2">
         <f>0/16</f>
@@ -2948,7 +2948,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B55" s="2">
         <f>1/10</f>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B56" s="2">
         <f>3/12</f>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="B57" s="2">
         <f>3/10</f>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B69" s="2">
         <f>32/96</f>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B73" s="2">
         <f>5/22</f>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3746,7 +3746,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B85" s="2">
         <f>4/18</f>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B87" s="2">
         <f>2/16</f>
@@ -3840,7 +3840,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3924,7 +3924,7 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4008,7 +4008,7 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4036,7 +4036,7 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4158,7 +4158,7 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4320,7 +4320,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4348,7 +4348,7 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4362,7 +4362,7 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -4502,7 +4502,7 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -4586,7 +4586,7 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -4642,7 +4642,7 @@
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -4712,7 +4712,7 @@
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -4726,7 +4726,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -4907,7 +4907,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -4949,7 +4949,7 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -4991,7 +4991,7 @@
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -5005,7 +5005,7 @@
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -5145,7 +5145,7 @@
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -5173,7 +5173,7 @@
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -5201,7 +5201,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -5215,7 +5215,7 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -5285,7 +5285,7 @@
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -5327,7 +5327,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -5366,7 +5366,7 @@
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -5455,7 +5455,7 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -5511,7 +5511,7 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -5567,7 +5567,7 @@
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -5805,7 +5805,7 @@
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -5819,7 +5819,7 @@
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -5847,7 +5847,7 @@
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -5917,7 +5917,7 @@
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -5931,7 +5931,7 @@
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -5998,7 +5998,7 @@
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -6124,7 +6124,7 @@
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
